--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N102_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N102_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>83.24483517507969</v>
+        <v>13.52728571595045</v>
       </c>
       <c r="D2" t="n">
-        <v>82.04012940144746</v>
+        <v>13.33152102773521</v>
       </c>
       <c r="E2" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F2" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>58.38666087715752</v>
+        <v>9.487832392538097</v>
       </c>
       <c r="D3" t="n">
-        <v>75.11483984911048</v>
+        <v>12.20616147548045</v>
       </c>
       <c r="E3" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F3" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>77.60742267477498</v>
+        <v>12.61120618465094</v>
       </c>
       <c r="D4" t="n">
-        <v>76.50152638622529</v>
+        <v>12.43149803776161</v>
       </c>
       <c r="E4" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F4" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>41.53673670531472</v>
+        <v>6.749719714613643</v>
       </c>
       <c r="D5" t="n">
-        <v>61.62919043865375</v>
+        <v>10.01474344628124</v>
       </c>
       <c r="E5" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F5" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>27.71695788846775</v>
+        <v>4.50400565687601</v>
       </c>
       <c r="D6" t="n">
-        <v>64.53988576799155</v>
+        <v>10.48773143729863</v>
       </c>
       <c r="E6" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F6" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>50.46276129759229</v>
+        <v>8.200198710858746</v>
       </c>
       <c r="D7" t="n">
-        <v>49.44278124765869</v>
+        <v>8.034451952744538</v>
       </c>
       <c r="E7" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F7" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>17.54870207292962</v>
+        <v>2.851664086851063</v>
       </c>
       <c r="D8" t="n">
-        <v>56.90138776347144</v>
+        <v>9.246475511564109</v>
       </c>
       <c r="E8" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F8" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>38.90224481310423</v>
+        <v>6.321614782129437</v>
       </c>
       <c r="D9" t="n">
-        <v>37.71625812160547</v>
+        <v>6.128891944760889</v>
       </c>
       <c r="E9" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F9" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.961941466289479</v>
+        <v>1.61881548827204</v>
       </c>
       <c r="D10" t="n">
-        <v>47.75326500975994</v>
+        <v>7.75990556408599</v>
       </c>
       <c r="E10" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F10" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.92575411079363</v>
+        <v>1.937935043003965</v>
       </c>
       <c r="D11" t="n">
-        <v>29</v>
+        <v>4.7125</v>
       </c>
       <c r="E11" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F11" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>45.43432378475305</v>
+        <v>7.383077615022372</v>
       </c>
       <c r="D12" t="n">
-        <v>51.72630966066602</v>
+        <v>8.405525319858228</v>
       </c>
       <c r="E12" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F12" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>20.3147729497526</v>
+        <v>3.301150604334798</v>
       </c>
       <c r="D13" t="n">
-        <v>17.34618113591577</v>
+        <v>2.818754434586312</v>
       </c>
       <c r="E13" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F13" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>27.49211088947963</v>
+        <v>4.467468019540441</v>
       </c>
       <c r="D14" t="n">
-        <v>21.73131381210073</v>
+        <v>3.531338494466369</v>
       </c>
       <c r="E14" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F14" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90348790056394</v>
+        <v>2.09681678384164</v>
       </c>
       <c r="D15" t="n">
-        <v>19.45507645834372</v>
+        <v>3.161449924480854</v>
       </c>
       <c r="E15" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F15" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>17.06604816587601</v>
+        <v>2.773232826954852</v>
       </c>
       <c r="D16" t="n">
-        <v>10.30776406404415</v>
+        <v>1.675011660407175</v>
       </c>
       <c r="E16" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F16" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>41.43179468851321</v>
+        <v>6.732666636883397</v>
       </c>
       <c r="D17" t="n">
-        <v>47.0619479457071</v>
+        <v>7.647566541177404</v>
       </c>
       <c r="E17" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F17" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>38.85337051016295</v>
+        <v>6.313672707901479</v>
       </c>
       <c r="D18" t="n">
-        <v>21.90326800748946</v>
+        <v>3.559281051217038</v>
       </c>
       <c r="E18" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F18" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>32.38826948140329</v>
+        <v>5.263093790728036</v>
       </c>
       <c r="D19" t="n">
-        <v>33.24154027718932</v>
+        <v>5.401750295043265</v>
       </c>
       <c r="E19" t="n">
-        <v>20.7201392186317</v>
+        <v>3.367022623027653</v>
       </c>
       <c r="F19" t="n">
-        <v>21.4587939777935</v>
+        <v>3.487054021391444</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
